--- a/src/main/resources/excel/Similares.xlsx
+++ b/src/main/resources/excel/Similares.xlsx
@@ -1117,12 +1117,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1159,16 +1165,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1302,6 +1312,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1325,7 +1336,7 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1350,7 +1361,7 @@
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1375,7 +1386,7 @@
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1400,7 +1411,7 @@
       <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1425,7 +1436,7 @@
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1450,7 +1461,7 @@
       <c r="D12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1475,7 +1486,7 @@
       <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1500,7 +1511,7 @@
       <c r="D16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1525,7 +1536,7 @@
       <c r="D18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1550,7 +1561,7 @@
       <c r="D20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1575,7 +1586,7 @@
       <c r="D22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1600,7 +1611,7 @@
       <c r="D24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1625,7 +1636,7 @@
       <c r="D26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1650,7 +1661,7 @@
       <c r="D28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1675,7 +1686,7 @@
       <c r="D30" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1700,7 +1711,7 @@
       <c r="D32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1725,7 +1736,7 @@
       <c r="D34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1750,7 +1761,7 @@
       <c r="D36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1775,7 +1786,7 @@
       <c r="D38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1800,7 +1811,7 @@
       <c r="D40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1825,7 +1836,7 @@
       <c r="D42" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1850,7 +1861,7 @@
       <c r="D44" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1872,11 +1883,10 @@
       <c r="B46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C46" s="0"/>
       <c r="D46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1899,7 +1909,9 @@
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1923,7 +1935,7 @@
       <c r="D2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1948,7 +1960,7 @@
       <c r="D4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1973,7 +1985,7 @@
       <c r="D6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1998,7 +2010,7 @@
       <c r="D8" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2023,7 +2035,7 @@
       <c r="D10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2048,7 +2060,7 @@
       <c r="D12" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2073,7 +2085,7 @@
       <c r="D14" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2098,7 +2110,7 @@
       <c r="D16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2123,7 +2135,7 @@
       <c r="D18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2148,7 +2160,7 @@
       <c r="D20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2173,7 +2185,7 @@
       <c r="D22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2198,7 +2210,7 @@
       <c r="D24" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2223,7 +2235,7 @@
       <c r="D26" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2248,7 +2260,7 @@
       <c r="D28" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2273,7 +2285,7 @@
       <c r="D30" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2298,7 +2310,7 @@
       <c r="D32" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2323,7 +2335,7 @@
       <c r="D34" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2348,7 +2360,7 @@
       <c r="D36" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2373,7 +2385,7 @@
       <c r="D38" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2398,7 +2410,7 @@
       <c r="D40" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2423,7 +2435,7 @@
       <c r="D42" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2448,7 +2460,7 @@
       <c r="D44" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2473,6 +2485,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2482,7 +2495,7 @@
       <c r="B1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2493,10 +2506,10 @@
       <c r="B2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2507,7 +2520,7 @@
       <c r="B3" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2518,10 +2531,10 @@
       <c r="B4" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2532,10 +2545,10 @@
       <c r="B5" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2546,7 +2559,7 @@
       <c r="B6" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>241</v>
       </c>
     </row>
@@ -2557,10 +2570,10 @@
       <c r="B7" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2571,7 +2584,7 @@
       <c r="B8" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>247</v>
       </c>
     </row>
@@ -2582,10 +2595,10 @@
       <c r="B9" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2596,10 +2609,10 @@
       <c r="B10" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2610,7 +2623,7 @@
       <c r="B11" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2621,10 +2634,10 @@
       <c r="B12" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2635,7 +2648,7 @@
       <c r="B13" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>259</v>
       </c>
     </row>
@@ -2646,10 +2659,10 @@
       <c r="B14" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2660,7 +2673,7 @@
       <c r="B15" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2674,7 +2687,7 @@
       <c r="D16" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2699,7 +2712,7 @@
       <c r="D18" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2724,7 +2737,7 @@
       <c r="D20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2749,7 +2762,7 @@
       <c r="D22" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2774,7 +2787,7 @@
       <c r="D24" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2799,7 +2812,7 @@
       <c r="D26" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2813,7 +2826,7 @@
       <c r="D27" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2838,7 +2851,7 @@
       <c r="D29" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2863,7 +2876,7 @@
       <c r="D31" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2888,7 +2901,7 @@
       <c r="D33" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2913,7 +2926,7 @@
       <c r="D35" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2938,7 +2951,7 @@
       <c r="D37" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2963,7 +2976,7 @@
       <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2988,7 +3001,7 @@
       <c r="D41" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3013,7 +3026,7 @@
       <c r="D43" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3038,7 +3051,7 @@
       <c r="D45" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3060,6 +3073,9 @@
   </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="11.53"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3082,7 +3098,7 @@
       <c r="D2" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3107,7 +3123,7 @@
       <c r="D4" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3132,7 +3148,7 @@
       <c r="D6" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3157,7 +3173,7 @@
       <c r="D8" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3182,7 +3198,7 @@
       <c r="D10" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3207,7 +3223,7 @@
       <c r="D12" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3221,7 +3237,7 @@
       <c r="D13" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3246,7 +3262,7 @@
       <c r="D15" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
